--- a/Automatic Bread Maker/Grading/2 stage/3-examples/Automatic-Bread-Maker_Grading_2-stage_2026-03-03_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Automatic Bread Maker/Grading/2 stage/3-examples/Automatic-Bread-Maker_Grading_2-stage_2026-03-03_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Automatic Bread Maker/Grading/2 stage/2026-03-03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Automatic Bread Maker/Grading/2 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4471411-7909-A646-B058-5B33FD13BC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB3FE3-B2B2-484C-84B4-37909C11D1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Automatic Bread Maker" sheetId="1" r:id="rId1"/>
@@ -659,7 +659,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -948,11 +948,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1153,19 +1162,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1517,12 +1529,20 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A1:D54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A1:D56">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Type"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Element"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Human"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="LLM"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Type">
+      <calculatedColumnFormula>'Automatic Bread Maker Human-Bas'!A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Element">
+      <calculatedColumnFormula>'Automatic Bread Maker Human-Bas'!B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Human">
+      <calculatedColumnFormula>'Automatic Bread Maker Human-Bas'!C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="LLM">
+      <calculatedColumnFormula>'Automatic Bread Maker LLM-Based'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Inter-rater-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17884,16 +17904,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
       <c r="J1" s="39" t="s">
         <v>113</v>
       </c>
@@ -18215,16 +18235,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40" t="s">
@@ -19540,33 +19560,33 @@
       <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="88" t="s">
+      <c r="D1" s="82" t="s">
         <v>167</v>
       </c>
       <c r="E1" s="49"/>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="L1" s="86" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="L1" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A3</f>
+        <f>'Automatic Bread Maker Human-Bas'!A2</f>
         <v>State</v>
       </c>
       <c r="B2" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B3</f>
-        <v>Off</v>
+        <f>'Automatic Bread Maker Human-Bas'!B2</f>
+        <v>Initial state (→ Off)</v>
       </c>
       <c r="C2" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C2</f>
@@ -19605,12 +19625,12 @@
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A4</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A3</f>
+        <v>State</v>
       </c>
       <c r="B3" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B4</f>
-        <v>on (Off ⇒ On)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B3</f>
+        <v>Off</v>
       </c>
       <c r="C3" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C3</f>
@@ -19625,28 +19645,28 @@
         <v>0</v>
       </c>
       <c r="G3" s="57">
-        <f>COUNTIFS($C$2:$C$91, $F3, $D$2:$D$91, G$2)</f>
-        <v>17</v>
+        <f>COUNTIFS($C$2:$C$93, $F3, $D$2:$D$93, G$2)</f>
+        <v>19</v>
       </c>
       <c r="H3" s="58">
-        <f>COUNTIFS($C$2:$C$47, $F3, $D$2:$D$47, H$2)</f>
+        <f>COUNTIFS($C$2:$C$49, $F3, $D$2:$D$49, H$2)</f>
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <f>COUNTIFS($C$2:$C$47, $F3, $D$2:$D$47, I$2)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)+MAX(D54-C54,0)</f>
+        <f>COUNTIFS($C$2:$C$49, $F3, $D$2:$D$49, I$2)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)+MAX(D54-C54,0)+MAX(D55-C55,0)+MAX(D56-C56,0)</f>
         <v>1</v>
       </c>
       <c r="J3" s="14">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K3" s="14"/>
       <c r="L3" s="60" t="s">
         <v>138</v>
       </c>
       <c r="M3" s="57">
-        <f>(G3+H4+I5)/COUNTA($C$2:$C$101)</f>
-        <v>0.92452830188679247</v>
+        <f>(G3+H4+I5)/COUNTA($C$2:$C$103)</f>
+        <v>0.92727272727272725</v>
       </c>
       <c r="N3" s="59" t="s">
         <v>139</v>
@@ -19654,12 +19674,12 @@
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A5</f>
-        <v>Composite State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A4</f>
+        <v>Transition</v>
       </c>
       <c r="B4" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B5</f>
-        <v>On</v>
+        <f>'Automatic Bread Maker Human-Bas'!B4</f>
+        <v>on (Off ⇒ On)</v>
       </c>
       <c r="C4" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C4</f>
@@ -19674,15 +19694,15 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="61">
-        <f t="shared" ref="G4:I4" si="1">COUNTIFS($C$2:$C$47, $F4, $D$2:$D$47, G$2)</f>
+        <f>COUNTIFS($C$2:$C$49, $F4, $D$2:$D$49, G$2)</f>
         <v>0</v>
       </c>
       <c r="H4" s="14">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$49, $F4, $D$2:$D$49, H$2)</f>
         <v>0</v>
       </c>
       <c r="I4" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$49, $F4, $D$2:$D$49, I$2)</f>
         <v>1</v>
       </c>
       <c r="J4" s="14">
@@ -19694,8 +19714,8 @@
         <v>140</v>
       </c>
       <c r="M4" s="61">
-        <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$101), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$101))</f>
-        <v>0.52723389106443574</v>
+        <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$103), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$103))</f>
+        <v>0.51471074380165294</v>
       </c>
       <c r="N4" s="62" t="s">
         <v>141</v>
@@ -19703,12 +19723,12 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A2</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A5</f>
+        <v>Composite State</v>
       </c>
       <c r="B5" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B2</f>
-        <v>Initial state (→ Off)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B5</f>
+        <v>On</v>
       </c>
       <c r="C5" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C5</f>
@@ -19723,15 +19743,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="63">
-        <f>COUNTIFS($C$2:$C$47, $F5, $D$2:$D$47, G$2)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)+MAX(C54-D54,0)</f>
+        <f>COUNTIFS($C$2:$C$49, $F5, $D$2:$D$49, G$2)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)+MAX(C54-D54,0)+MAX(C55-D55,0)+MAX(C56-D56,0)</f>
         <v>1</v>
       </c>
       <c r="H5" s="64">
-        <f>COUNTIFS($C$2:$C$47, $F5, $D$2:$D$47, H$2)</f>
+        <f>COUNTIFS($C$2:$C$49, $F5, $D$2:$D$49, H$2)</f>
         <v>1</v>
       </c>
       <c r="I5" s="65">
-        <f>COUNTIFS($C$2:$C$47, $F5, $D$2:$D$47, I$2)+ SUM(MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53), MIN(C54,D54))</f>
+        <f>COUNTIFS($C$2:$C$49, $F5, $D$2:$D$49, I$2)+ SUM(MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53), MIN(C54,D54), MIN(C55,D55), MIN(C56,D56))</f>
         <v>32</v>
       </c>
       <c r="J5" s="14">
@@ -19744,7 +19764,7 @@
       </c>
       <c r="M5" s="63">
         <f>(M3-M4)/(1-M4)</f>
-        <v>0.84036144578313254</v>
+        <v>0.85013623978201625</v>
       </c>
       <c r="N5" s="65" t="s">
         <v>142</v>
@@ -19752,12 +19772,12 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A7</f>
-        <v>Composite State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A6</f>
+        <v>Transition</v>
       </c>
       <c r="B6" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B7</f>
-        <v>Setup</v>
+        <f>'Automatic Bread Maker Human-Bas'!B6</f>
+        <v>on =&gt; off</v>
       </c>
       <c r="C6" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C6</f>
@@ -19772,15 +19792,15 @@
         <v>143</v>
       </c>
       <c r="G6" s="14">
-        <f t="shared" ref="G6:I6" si="2">SUM(G3:G5)</f>
-        <v>18</v>
+        <f t="shared" ref="G6:I6" si="1">SUM(G3:G5)</f>
+        <v>20</v>
       </c>
       <c r="H6" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I6" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="J6" s="14"/>
@@ -19789,12 +19809,12 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A8</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A7</f>
+        <v>Composite State</v>
       </c>
       <c r="B7" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B8</f>
-        <v>Initial state (Setup → Medium)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B7</f>
+        <v>Setup</v>
       </c>
       <c r="C7" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C7</f>
@@ -19811,42 +19831,42 @@
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A8</f>
+        <v>State</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B8</f>
+        <v>Initial state (Setup → Medium)</v>
+      </c>
+      <c r="C8" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C8</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="L8" s="87" t="s">
+        <v>145</v>
+      </c>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A9</f>
         <v>Action</v>
       </c>
-      <c r="B8" s="5" t="str">
+      <c r="B9" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B9</f>
         <v>delay=0; selectFirstCourse()</v>
-      </c>
-      <c r="C8" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C8</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="84" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="L8" s="86" t="s">
-        <v>145</v>
-      </c>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A10</f>
-        <v>State</v>
-      </c>
-      <c r="B9" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B10</f>
-        <v>Medium</v>
       </c>
       <c r="C9" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C9</f>
@@ -19885,12 +19905,12 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A11</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A10</f>
+        <v>State</v>
       </c>
       <c r="B10" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B11</f>
-        <v>setup initial state =&gt; medium</v>
+        <f>'Automatic Bread Maker Human-Bas'!B10</f>
+        <v>Medium</v>
       </c>
       <c r="C10" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C10</f>
@@ -19905,28 +19925,28 @@
         <v>0</v>
       </c>
       <c r="G10" s="57">
-        <f t="shared" ref="G10:H10" si="3">COUNTIFS($A$2:$A$91,$F$9,$C$2:$C$91,$F10,$D$2:$D$91,G$9)</f>
-        <v>3</v>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F10,$D$2:$D$93,G$9)</f>
+        <v>5</v>
       </c>
       <c r="H10" s="58">
-        <f t="shared" si="3"/>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F10,$D$2:$D$93,H$9)</f>
         <v>0</v>
       </c>
       <c r="I10" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$9,$C$2:$C$47,$F10,$D$2:$D$47,I$9)+MAX(D48-C48,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$9,$C$2:$C$49,$F10,$D$2:$D$49,I$9)+MAX(D50-C50,0)</f>
         <v>0</v>
       </c>
       <c r="J10" s="14">
-        <f t="shared" ref="J10:J12" si="4">SUM(G10:I10)</f>
-        <v>3</v>
+        <f t="shared" ref="J10:J12" si="2">SUM(G10:I10)</f>
+        <v>5</v>
       </c>
       <c r="K10" s="14"/>
       <c r="L10" s="60" t="s">
         <v>138</v>
       </c>
       <c r="M10" s="57">
-        <f>(G10+H11+I12)/COUNTIF($A$2:$A$101,F9)</f>
-        <v>0.84615384615384615</v>
+        <f>(G10+H11+I12)/COUNTIF($A$2:$A$103,F9)</f>
+        <v>1</v>
       </c>
       <c r="N10" s="59" t="s">
         <v>139</v>
@@ -19934,12 +19954,12 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A12</f>
+        <f>'Automatic Bread Maker Human-Bas'!A11</f>
         <v>Transition</v>
       </c>
       <c r="B11" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B12</f>
-        <v>medium =&gt; dark</v>
+        <f>'Automatic Bread Maker Human-Bas'!B11</f>
+        <v>setup initial state =&gt; medium</v>
       </c>
       <c r="C11" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C11</f>
@@ -19954,19 +19974,19 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="61">
-        <f t="shared" ref="G11:I11" si="5">COUNTIFS($A$2:$A$91,$F$9,$C$2:$C$91,$F11,$D$2:$D$91,G$9)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F11,$D$2:$D$93,G$9)</f>
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <f t="shared" si="5"/>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F11,$D$2:$D$93,H$9)</f>
         <v>0</v>
       </c>
       <c r="I11" s="62">
-        <f t="shared" si="5"/>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F11,$D$2:$D$93,I$9)</f>
         <v>0</v>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="14"/>
@@ -19974,8 +19994,8 @@
         <v>140</v>
       </c>
       <c r="M11" s="61">
-        <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTIF($A$2:$A$101,F9), TRANSPOSE(G13:I13)/COUNTIF($A$2:$A$101,F9))</f>
-        <v>0.47928994082840237</v>
+        <f t="array" ref="M11">SUMPRODUCT(J10:J12/COUNTIF($A$2:$A$103,F9), TRANSPOSE(G13:I13)/COUNTIF($A$2:$A$103,F9))</f>
+        <v>0.52662721893491127</v>
       </c>
       <c r="N11" s="62" t="s">
         <v>141</v>
@@ -19983,12 +20003,12 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A13</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A12</f>
+        <v>Transition</v>
       </c>
       <c r="B12" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B13</f>
-        <v>Dark</v>
+        <f>'Automatic Bread Maker Human-Bas'!B12</f>
+        <v>medium =&gt; dark</v>
       </c>
       <c r="C12" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C12</f>
@@ -20003,20 +20023,20 @@
         <v>1</v>
       </c>
       <c r="G12" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$9,$C$2:$C$47,$F12,$D$2:$D$47,G$9)+MAX(C48-D48,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$9,$C$2:$C$49,$F12,$D$2:$D$49,G$9)+MAX(C50-D50,0)</f>
         <v>0</v>
       </c>
       <c r="H12" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$9,$C$2:$C$91,$F12,$D$2:$D$91,H$9)</f>
-        <v>1</v>
+        <f>COUNTIFS($A$2:$A$93,$F$9,$C$2:$C$93,$F12,$D$2:$D$93,H$9)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$9,$C$2:$C$47,$F12,$D$2:$D$47,I$9)+MIN(C48-D48)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$9,$C$2:$C$49,$F12,$D$2:$D$49,I$9)+MIN(C50-D50)</f>
         <v>8</v>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="K12" s="14"/>
       <c r="L12" s="60" t="s">
@@ -20024,7 +20044,7 @@
       </c>
       <c r="M12" s="63">
         <f>(M10-M11)/(1-M11)</f>
-        <v>0.70454545454545447</v>
+        <v>1</v>
       </c>
       <c r="N12" s="65" t="s">
         <v>142</v>
@@ -20032,12 +20052,12 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A14</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A13</f>
+        <v>State</v>
       </c>
       <c r="B13" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B14</f>
-        <v>dark =&gt; light</v>
+        <f>'Automatic Bread Maker Human-Bas'!B13</f>
+        <v>Dark</v>
       </c>
       <c r="C13" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C13</f>
@@ -20052,15 +20072,15 @@
         <v>143</v>
       </c>
       <c r="G13" s="14">
-        <f t="shared" ref="G13:I13" si="6">SUM(G10:G12)</f>
-        <v>3</v>
+        <f t="shared" ref="G13:I13" si="3">SUM(G10:G12)</f>
+        <v>5</v>
       </c>
       <c r="H13" s="14">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="J13" s="14"/>
@@ -20069,61 +20089,61 @@
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A14</f>
+        <v>Transition</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B14</f>
+        <v>dark =&gt; light</v>
+      </c>
+      <c r="C14" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C14</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="49"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A15</f>
         <v>State</v>
       </c>
-      <c r="B14" s="5" t="str">
+      <c r="B15" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B15</f>
         <v>Light</v>
       </c>
-      <c r="C14" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C14</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="49"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="str">
+      <c r="C15" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C15</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="49"/>
+      <c r="F15" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="L15" s="87" t="s">
+        <v>147</v>
+      </c>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A16</f>
         <v>History State</v>
       </c>
-      <c r="B15" s="5" t="str">
+      <c r="B16" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B16</f>
         <v>H</v>
-      </c>
-      <c r="C15" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C15</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="84" t="s">
-        <v>146</v>
-      </c>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
-      <c r="L15" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="M15" s="87"/>
-      <c r="N15" s="87"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A17</f>
-        <v>Transition</v>
-      </c>
-      <c r="B16" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B17</f>
-        <v>setup =&gt; H</v>
       </c>
       <c r="C16" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C16</f>
@@ -20162,12 +20182,12 @@
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A18</f>
-        <v>Action</v>
+        <f>'Automatic Bread Maker Human-Bas'!A17</f>
+        <v>Transition</v>
       </c>
       <c r="B17" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B18</f>
-        <v>selectNextCourse()</v>
+        <f>'Automatic Bread Maker Human-Bas'!B17</f>
+        <v>setup =&gt; H</v>
       </c>
       <c r="C17" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C17</f>
@@ -20182,19 +20202,19 @@
         <v>0</v>
       </c>
       <c r="G17" s="57">
-        <f t="shared" ref="G17:H17" si="7">COUNTIFS($A$2:$A$91,$F$16,$C$2:$C$91,$F17,$D$2:$D$91,G$16)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F17,$D$2:$D$93,G$16)</f>
         <v>5</v>
       </c>
       <c r="H17" s="58">
-        <f t="shared" si="7"/>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F17,$D$2:$D$93,H$16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$16,$C$2:$C$47,$F17,$D$2:$D$47,I$16) + MAX(D49-C49,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$16,$C$2:$C$49,$F17,$D$2:$D$49,I$16) + MAX(D51-C51,0)</f>
         <v>1</v>
       </c>
       <c r="J17" s="14">
-        <f t="shared" ref="J17:J19" si="8">SUM(G17:I17)</f>
+        <f t="shared" ref="J17:J19" si="4">SUM(G17:I17)</f>
         <v>6</v>
       </c>
       <c r="K17" s="14"/>
@@ -20202,8 +20222,8 @@
         <v>138</v>
       </c>
       <c r="M17" s="57">
-        <f>(G17+H18+I19)/COUNTIF($A$2:$A$101,F16)</f>
-        <v>0.88235294117647056</v>
+        <f>(G17+H18+I19)/COUNTIF($A$2:$A$103,F16)</f>
+        <v>0.89473684210526316</v>
       </c>
       <c r="N17" s="59" t="s">
         <v>139</v>
@@ -20211,12 +20231,12 @@
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A19</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A18</f>
+        <v>Action</v>
       </c>
       <c r="B18" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B19</f>
-        <v>plus (Setup ⇒ Setup)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B18</f>
+        <v>selectNextCourse()</v>
       </c>
       <c r="C18" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C18</f>
@@ -20231,28 +20251,28 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="61">
-        <f t="shared" ref="G18:I18" si="9">COUNTIFS($A$2:$A$91,$F$16,$C$2:$C$91,$F18,$D$2:$D$91,G$16)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F18,$D$2:$D$93,G$16)</f>
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <f t="shared" si="9"/>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F18,$D$2:$D$93,H$16)</f>
         <v>0</v>
       </c>
       <c r="I18" s="62">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F18,$D$2:$D$93,I$16)</f>
+        <v>1</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K18" s="14"/>
       <c r="L18" s="60" t="s">
         <v>140</v>
       </c>
       <c r="M18" s="61">
-        <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$101,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$101,F16))</f>
-        <v>0.54325259515570945</v>
+        <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$103,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$103,F16))</f>
+        <v>0.54847645429362879</v>
       </c>
       <c r="N18" s="62" t="s">
         <v>141</v>
@@ -20260,12 +20280,12 @@
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A20</f>
-        <v>Guard</v>
+        <f>'Automatic Bread Maker Human-Bas'!A19</f>
+        <v>Transition</v>
       </c>
       <c r="B19" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B20</f>
-        <v>[delay &lt;= 17*60+50]</v>
+        <f>'Automatic Bread Maker Human-Bas'!B19</f>
+        <v>plus (Setup ⇒ Setup)</v>
       </c>
       <c r="C19" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C19</f>
@@ -20280,20 +20300,20 @@
         <v>1</v>
       </c>
       <c r="G19" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$16,$C$2:$C$47,$F19,$D$2:$D$47,G$16)+MAX(C49-D49,0)</f>
-        <v>1</v>
+        <f>COUNTIFS($A$2:$A$49,$F$16,$C$2:$C$49,$F19,$D$2:$D$49,G$16)+MAX(C51-D51,0)</f>
+        <v>0</v>
       </c>
       <c r="H19" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$16,$C$2:$C$91,$F19,$D$2:$D$91,H$16)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$16,$C$2:$C$93,$F19,$D$2:$D$93,H$16)</f>
         <v>0</v>
       </c>
       <c r="I19" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$16,$C$2:$C$47,$F19,$D$2:$D$47,I$16) + MIN(C49,D49)</f>
-        <v>10</v>
+        <f>COUNTIFS($A$2:$A$49,$F$16,$C$2:$C$49,$F19,$D$2:$D$49,I$16) + MIN(C51,D51)</f>
+        <v>12</v>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f t="shared" si="4"/>
+        <v>12</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="60" t="s">
@@ -20301,7 +20321,7 @@
       </c>
       <c r="M19" s="63">
         <f>(M17-M18)/(1-M18)</f>
-        <v>0.74242424242424232</v>
+        <v>0.76687116564417179</v>
       </c>
       <c r="N19" s="65" t="s">
         <v>142</v>
@@ -20309,12 +20329,12 @@
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A21</f>
-        <v>Action</v>
+        <f>'Automatic Bread Maker Human-Bas'!A20</f>
+        <v>Guard</v>
       </c>
       <c r="B20" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B21</f>
-        <v>delay = delay + 10</v>
+        <f>'Automatic Bread Maker Human-Bas'!B20</f>
+        <v>[delay &lt;= 17*60+50]</v>
       </c>
       <c r="C20" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C20</f>
@@ -20329,16 +20349,16 @@
         <v>143</v>
       </c>
       <c r="G20" s="14">
-        <f t="shared" ref="G20:I20" si="10">SUM(G17:G19)</f>
-        <v>6</v>
+        <f t="shared" ref="G20:I20" si="5">SUM(G17:G19)</f>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f t="shared" si="10"/>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>14</v>
       </c>
       <c r="J20" s="14"/>
       <c r="L20" s="14"/>
@@ -20346,61 +20366,61 @@
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A21</f>
+        <v>Action</v>
+      </c>
+      <c r="B21" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B21</f>
+        <v>delay = delay + 10</v>
+      </c>
+      <c r="C21" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C21</f>
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C21</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="49"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A22</f>
         <v>Transition</v>
       </c>
-      <c r="B21" s="5" t="str">
+      <c r="B22" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B22</f>
         <v>minus (Setup ⇒ Setup)</v>
       </c>
-      <c r="C21" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C21</f>
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C21</f>
-        <v>1</v>
-      </c>
-      <c r="E21" s="49"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="str">
+      <c r="C22" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C22</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C22</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="49"/>
+      <c r="F22" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="L22" s="87" t="s">
+        <v>149</v>
+      </c>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A23</f>
         <v>Guard</v>
       </c>
-      <c r="B22" s="5" t="str">
+      <c r="B23" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B23</f>
         <v>[delay &gt;= 10]</v>
-      </c>
-      <c r="C22" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C22</f>
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C22</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="49"/>
-      <c r="F22" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="L22" s="86" t="s">
-        <v>149</v>
-      </c>
-      <c r="M22" s="87"/>
-      <c r="N22" s="87"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A24</f>
-        <v>Action</v>
-      </c>
-      <c r="B23" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B24</f>
-        <v>delay = delay - 10</v>
       </c>
       <c r="C23" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C23</f>
@@ -20439,12 +20459,12 @@
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A25</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A24</f>
+        <v>Action</v>
       </c>
       <c r="B24" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B25</f>
-        <v>start (Setup ⇒ Countdown)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B24</f>
+        <v>delay = delay - 10</v>
       </c>
       <c r="C24" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C24</f>
@@ -20459,28 +20479,28 @@
         <v>0</v>
       </c>
       <c r="G24" s="57">
-        <f t="shared" ref="G24:H24" si="11">COUNTIFS($A$2:$A$91,$F$23,$C$2:$C$91,$F24,$D$2:$D$91,G$23)</f>
-        <v>2</v>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F24,$D$2:$D$93,G$23)</f>
+        <v>1</v>
       </c>
       <c r="H24" s="58">
-        <f t="shared" si="11"/>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F24,$D$2:$D$93,H$23)</f>
         <v>0</v>
       </c>
       <c r="I24" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$23,$C$2:$C$47,$F24,$D$2:$D$47,I$23) + MAX(D52-C52,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$23,$C$2:$C$49,$F24,$D$2:$D$49,I$23) + MAX(D54-C54,0)</f>
         <v>0</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" ref="J24:J26" si="12">SUM(G24:I24)</f>
-        <v>2</v>
+        <f t="shared" ref="J24:J26" si="6">SUM(G24:I24)</f>
+        <v>1</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="60" t="s">
         <v>138</v>
       </c>
       <c r="M24" s="57">
-        <f>(G24+H25+I26)/COUNTIF($A$2:$A$101,F23)</f>
-        <v>1</v>
+        <f>(G24+H25+I26)/COUNTIF($A$2:$A$103,F23)</f>
+        <v>0.75</v>
       </c>
       <c r="N24" s="59" t="s">
         <v>139</v>
@@ -20488,12 +20508,12 @@
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A26</f>
-        <v>Guard</v>
+        <f>'Automatic Bread Maker Human-Bas'!A25</f>
+        <v>Transition</v>
       </c>
       <c r="B25" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B26</f>
-        <v>[delay &gt; 0]</v>
+        <f>'Automatic Bread Maker Human-Bas'!B25</f>
+        <v>start (Setup ⇒ Countdown)</v>
       </c>
       <c r="C25" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C25</f>
@@ -20508,19 +20528,19 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="61">
-        <f t="shared" ref="G25:I25" si="13">COUNTIFS($A$2:$A$91,$F$23,$C$2:$C$91,$F25,$D$2:$D$91,G$23)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F25,$D$2:$D$93,G$23)</f>
         <v>0</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="13"/>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F25,$D$2:$D$93,H$23)</f>
         <v>0</v>
       </c>
       <c r="I25" s="62">
-        <f t="shared" si="13"/>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F25,$D$2:$D$93,I$23)</f>
         <v>0</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K25" s="14"/>
@@ -20528,8 +20548,8 @@
         <v>140</v>
       </c>
       <c r="M25" s="61">
-        <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$101,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$101,F23))</f>
-        <v>0.5</v>
+        <f t="array" ref="M25">SUMPRODUCT(J24:J26/COUNTIF($A$2:$A$103,F23), TRANSPOSE(G27:I27)/COUNTIF($A$2:$A$103,F23))</f>
+        <v>0.4375</v>
       </c>
       <c r="N25" s="62" t="s">
         <v>141</v>
@@ -20537,12 +20557,12 @@
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A27</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A26</f>
+        <v>Guard</v>
       </c>
       <c r="B26" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B27</f>
-        <v>start (Setup ⇒ Baking)</v>
+        <f>'Automatic Bread Maker Human-Bas'!B26</f>
+        <v>[delay &gt; 0]</v>
       </c>
       <c r="C26" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C26</f>
@@ -20557,20 +20577,20 @@
         <v>1</v>
       </c>
       <c r="G26" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$23,$C$2:$C$47,$F26,$D$2:$D$47,G$23) + MAX(C52-D52,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$23,$C$2:$C$49,$F26,$D$2:$D$49,G$23) + MAX(C54-D54,0)</f>
         <v>0</v>
       </c>
       <c r="H26" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$23,$C$2:$C$91,$F26,$D$2:$D$91,H$23)</f>
-        <v>0</v>
+        <f>COUNTIFS($A$2:$A$93,$F$23,$C$2:$C$93,$F26,$D$2:$D$93,H$23)</f>
+        <v>1</v>
       </c>
       <c r="I26" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$23,$C$2:$C$47,$F26,$D$2:$D$47,I$23) + MIN(C52,D52)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$23,$C$2:$C$49,$F26,$D$2:$D$49,I$23) + MIN(C54,D54)</f>
         <v>2</v>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="12"/>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="K26" s="14"/>
       <c r="L26" s="60" t="s">
@@ -20578,7 +20598,7 @@
       </c>
       <c r="M26" s="63">
         <f>(M24-M25)/(1-M25)</f>
-        <v>1</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="N26" s="65" t="s">
         <v>142</v>
@@ -20586,12 +20606,12 @@
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A28</f>
-        <v>Guard</v>
+        <f>'Automatic Bread Maker Human-Bas'!A27</f>
+        <v>Transition</v>
       </c>
       <c r="B27" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B28</f>
-        <v>[delay == 0]</v>
+        <f>'Automatic Bread Maker Human-Bas'!B27</f>
+        <v>start (Setup ⇒ Baking)</v>
       </c>
       <c r="C27" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C27</f>
@@ -20606,15 +20626,15 @@
         <v>143</v>
       </c>
       <c r="G27" s="14">
-        <f t="shared" ref="G27:I27" si="14">SUM(G24:G26)</f>
-        <v>2</v>
+        <f t="shared" ref="G27:I27" si="7">SUM(G24:G26)</f>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="J27" s="14"/>
@@ -20623,61 +20643,61 @@
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A28</f>
+        <v>Guard</v>
+      </c>
+      <c r="B28" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B28</f>
+        <v>[delay == 0]</v>
+      </c>
+      <c r="C28" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C28</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C28</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A29</f>
         <v>State</v>
       </c>
-      <c r="B28" s="5" t="str">
+      <c r="B29" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B29</f>
         <v>Countdown</v>
       </c>
-      <c r="C28" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C28</f>
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C28</f>
-        <v>1</v>
-      </c>
-      <c r="E28" s="49"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="str">
+      <c r="C29" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C29</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C29</f>
+        <v>1</v>
+      </c>
+      <c r="E29" s="49"/>
+      <c r="F29" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="L29" s="87" t="s">
+        <v>151</v>
+      </c>
+      <c r="M29" s="88"/>
+      <c r="N29" s="88"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A30</f>
         <v>Action</v>
       </c>
-      <c r="B29" s="5" t="str">
+      <c r="B30" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B30</f>
         <v>setCourseTimes()</v>
-      </c>
-      <c r="C29" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C29</f>
-        <v>1</v>
-      </c>
-      <c r="D29" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C29</f>
-        <v>1</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="84" t="s">
-        <v>150</v>
-      </c>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="L29" s="86" t="s">
-        <v>151</v>
-      </c>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A31</f>
-        <v>Transition</v>
-      </c>
-      <c r="B30" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B31</f>
-        <v>Countdown =&gt; baking</v>
       </c>
       <c r="C30" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C30</f>
@@ -20716,12 +20736,12 @@
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A32</f>
+        <f>'Automatic Bread Maker Human-Bas'!A31</f>
         <v>Transition</v>
       </c>
       <c r="B31" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B32</f>
-        <v>Countdown =&gt; setup</v>
+        <f>'Automatic Bread Maker Human-Bas'!B31</f>
+        <v>Countdown =&gt; baking</v>
       </c>
       <c r="C31" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C31</f>
@@ -20736,19 +20756,19 @@
         <v>0</v>
       </c>
       <c r="G31" s="57">
-        <f t="shared" ref="G31:H31" si="15">COUNTIFS($A$2:$A$91,$F$30,$C$2:$C$91,$F31,$D$2:$D$91,G$30)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F31,$D$2:$D$93,G$30)</f>
         <v>1</v>
       </c>
       <c r="H31" s="58">
-        <f t="shared" si="15"/>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F31,$D$2:$D$93,H$30)</f>
         <v>0</v>
       </c>
       <c r="I31" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$30,$C$2:$C$47,$F31,$D$2:$D$47,I$30) + MAX(D50-C50,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$30,$C$2:$C$49,$F31,$D$2:$D$49,I$30) + MAX(D52-C52,0)</f>
         <v>0</v>
       </c>
       <c r="J31" s="14">
-        <f t="shared" ref="J31:J33" si="16">SUM(G31:I31)</f>
+        <f t="shared" ref="J31:J33" si="8">SUM(G31:I31)</f>
         <v>1</v>
       </c>
       <c r="K31" s="14"/>
@@ -20756,8 +20776,8 @@
         <v>138</v>
       </c>
       <c r="M31" s="57">
-        <f>(G31+H32+I33)/COUNTIF($A$2:$A$101,F30)</f>
-        <v>0.8</v>
+        <f>(G31+H32+I33)/COUNTIF($A$2:$A$103,F30)</f>
+        <v>1</v>
       </c>
       <c r="N31" s="59" t="s">
         <v>139</v>
@@ -20765,12 +20785,12 @@
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A33</f>
-        <v>Action</v>
+        <f>'Automatic Bread Maker Human-Bas'!A32</f>
+        <v>Transition</v>
       </c>
       <c r="B32" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B33</f>
-        <v>setCourseTimes()</v>
+        <f>'Automatic Bread Maker Human-Bas'!B32</f>
+        <v>Countdown =&gt; setup</v>
       </c>
       <c r="C32" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C32</f>
@@ -20785,41 +20805,41 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="61">
-        <f t="shared" ref="G32:I32" si="17">COUNTIFS($A$2:$A$91,$F$30,$C$2:$C$91,$F32,$D$2:$D$91,G$30)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F32,$D$2:$D$93,G$30)</f>
         <v>0</v>
       </c>
       <c r="H32" s="14">
-        <f t="shared" si="17"/>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F32,$D$2:$D$93,H$30)</f>
         <v>0</v>
       </c>
       <c r="I32" s="62">
-        <f t="shared" si="17"/>
-        <v>1</v>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F32,$D$2:$D$93,I$30)</f>
+        <v>0</v>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="16"/>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="K32" s="14"/>
       <c r="L32" s="60" t="s">
         <v>140</v>
       </c>
       <c r="M32" s="61">
-        <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$101,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$101,F30))</f>
-        <v>0.52</v>
+        <f t="array" ref="M32">SUMPRODUCT(J31:J33/COUNTIF($A$2:$A$103,F30), TRANSPOSE(G34:I34)/COUNTIF($A$2:$A$103,F30))</f>
+        <v>0.68000000000000016</v>
       </c>
       <c r="N32" s="62" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A34</f>
-        <v>Composite State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A33</f>
+        <v>Action</v>
       </c>
       <c r="B33" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B34</f>
-        <v>Baking</v>
+        <f>'Automatic Bread Maker Human-Bas'!B33</f>
+        <v>setCourseTimes()</v>
       </c>
       <c r="C33" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C33</f>
@@ -20834,20 +20854,20 @@
         <v>1</v>
       </c>
       <c r="G33" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$30,$C$2:$C$47,$F33,$D$2:$D$47,G$30) + MAX(C50-D50,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$30,$C$2:$C$49,$F33,$D$2:$D$49,G$30) + MAX(C52-D52,0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$30,$C$2:$C$91,$F33,$D$2:$D$91,H$30)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$30,$C$2:$C$93,$F33,$D$2:$D$93,H$30)</f>
         <v>0</v>
       </c>
       <c r="I33" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$30,$C$2:$C$47,$F33,$D$2:$D$47,I$30) + MIN(C50,D50)</f>
-        <v>3</v>
+        <f>COUNTIFS($A$2:$A$49,$F$30,$C$2:$C$49,$F33,$D$2:$D$49,I$30) + MIN(C52,D52)</f>
+        <v>4</v>
       </c>
       <c r="J33" s="14">
-        <f t="shared" si="16"/>
-        <v>3</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="K33" s="14"/>
       <c r="L33" s="60" t="s">
@@ -20855,7 +20875,7 @@
       </c>
       <c r="M33" s="63">
         <f>(M31-M32)/(1-M32)</f>
-        <v>0.58333333333333337</v>
+        <v>1</v>
       </c>
       <c r="N33" s="65" t="s">
         <v>142</v>
@@ -20863,12 +20883,12 @@
     </row>
     <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A35</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A34</f>
+        <v>Composite State</v>
       </c>
       <c r="B34" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B35</f>
-        <v>Initial state</v>
+        <f>'Automatic Bread Maker Human-Bas'!B34</f>
+        <v>Baking</v>
       </c>
       <c r="C34" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C34</f>
@@ -20883,15 +20903,15 @@
         <v>143</v>
       </c>
       <c r="G34" s="14">
-        <f t="shared" ref="G34:I34" si="18">SUM(G31:G33)</f>
+        <f t="shared" ref="G34:I34" si="9">SUM(G31:G33)</f>
         <v>1</v>
       </c>
       <c r="H34" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J34" s="14"/>
@@ -20900,61 +20920,61 @@
     </row>
     <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A35</f>
+        <v>State</v>
+      </c>
+      <c r="B35" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B35</f>
+        <v>Initial state</v>
+      </c>
+      <c r="C35" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C35</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C35</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="49"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A36</f>
         <v>State</v>
       </c>
-      <c r="B35" s="5" t="str">
+      <c r="B36" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B36</f>
         <v>Kneading</v>
       </c>
-      <c r="C35" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C35</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C35</f>
-        <v>1</v>
-      </c>
-      <c r="E35" s="49"/>
-    </row>
-    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="5" t="str">
+      <c r="C36" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C36</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C36</f>
+        <v>1</v>
+      </c>
+      <c r="E36" s="49"/>
+      <c r="F36" s="83" t="s">
+        <v>152</v>
+      </c>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="L36" s="87" t="s">
+        <v>153</v>
+      </c>
+      <c r="M36" s="88"/>
+      <c r="N36" s="88"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A37</f>
         <v>Action</v>
       </c>
-      <c r="B36" s="5" t="str">
+      <c r="B37" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B37</f>
         <v>startKneading()</v>
-      </c>
-      <c r="C36" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C36</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C36</f>
-        <v>1</v>
-      </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="84" t="s">
-        <v>152</v>
-      </c>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="L36" s="86" t="s">
-        <v>153</v>
-      </c>
-      <c r="M36" s="87"/>
-      <c r="N36" s="87"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A38</f>
-        <v>Action</v>
-      </c>
-      <c r="B37" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B38</f>
-        <v>stopKneading()</v>
       </c>
       <c r="C37" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C37</f>
@@ -20993,12 +21013,12 @@
     </row>
     <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A39</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A38</f>
+        <v>Action</v>
       </c>
       <c r="B38" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B39</f>
-        <v>baking initial state =&gt; kneading</v>
+        <f>'Automatic Bread Maker Human-Bas'!B38</f>
+        <v>stopKneading()</v>
       </c>
       <c r="C38" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C38</f>
@@ -21013,28 +21033,28 @@
         <v>0</v>
       </c>
       <c r="G38" s="57">
-        <f t="shared" ref="G38:H38" si="19">COUNTIFS($A$2:$A$91,$F$37,$C$2:$C$91,$F38,$D$2:$D$91,G$37)</f>
-        <v>3</v>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F38,$D$2:$D$93,G$37)</f>
+        <v>4</v>
       </c>
       <c r="H38" s="58">
-        <f t="shared" si="19"/>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F38,$D$2:$D$93,H$37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$37,$C$2:$C$47,$F38,$D$2:$D$47,I$37)+MAX(D51-C51,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$37,$C$2:$C$49,$F38,$D$2:$D$49,I$37)+MAX(D53-C53,0)</f>
         <v>0</v>
       </c>
       <c r="J38" s="14">
-        <f t="shared" ref="J38:J40" si="20">SUM(G38:I38)</f>
-        <v>3</v>
+        <f t="shared" ref="J38:J40" si="10">SUM(G38:I38)</f>
+        <v>4</v>
       </c>
       <c r="K38" s="14"/>
       <c r="L38" s="60" t="s">
         <v>138</v>
       </c>
       <c r="M38" s="57">
-        <f>(G38+H39+I40)/COUNTIF($A$2:$A$101,F37)</f>
-        <v>1</v>
+        <f>(G38+H39+I40)/COUNTIF($A$2:$A$103,F37)</f>
+        <v>0.90909090909090906</v>
       </c>
       <c r="N38" s="59" t="s">
         <v>139</v>
@@ -21042,12 +21062,12 @@
     </row>
     <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A40</f>
+        <f>'Automatic Bread Maker Human-Bas'!A39</f>
         <v>Transition</v>
       </c>
       <c r="B39" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B40</f>
-        <v>kneading =&gt; rising</v>
+        <f>'Automatic Bread Maker Human-Bas'!B39</f>
+        <v>baking initial state =&gt; kneading</v>
       </c>
       <c r="C39" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C39</f>
@@ -21062,19 +21082,19 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="61">
-        <f t="shared" ref="G39:I39" si="21">COUNTIFS($A$2:$A$91,$F$37,$C$2:$C$91,$F39,$D$2:$D$91,G$37)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F39,$D$2:$D$93,G$37)</f>
         <v>0</v>
       </c>
       <c r="H39" s="14">
-        <f t="shared" si="21"/>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F39,$D$2:$D$93,H$37)</f>
         <v>0</v>
       </c>
       <c r="I39" s="62">
-        <f t="shared" si="21"/>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F39,$D$2:$D$93,I$37)</f>
         <v>0</v>
       </c>
       <c r="J39" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K39" s="14"/>
@@ -21082,21 +21102,21 @@
         <v>140</v>
       </c>
       <c r="M39" s="61">
-        <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$101,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$101,F37))</f>
-        <v>0.60330578512396693</v>
+        <f t="array" ref="M39">SUMPRODUCT(J38:J40/COUNTIF($A$2:$A$103,F37), TRANSPOSE(G41:I41)/COUNTIF($A$2:$A$103,F37))</f>
+        <v>0.51239669421487599</v>
       </c>
       <c r="N39" s="62" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A41</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A40</f>
+        <v>Transition</v>
       </c>
       <c r="B40" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B41</f>
-        <v>Rising</v>
+        <f>'Automatic Bread Maker Human-Bas'!B40</f>
+        <v>kneading =&gt; rising</v>
       </c>
       <c r="C40" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C40</f>
@@ -21111,20 +21131,20 @@
         <v>1</v>
       </c>
       <c r="G40" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$37,$C$2:$C$47,$F40,$D$2:$D$47,G$37)+MAX(C51-D51,0)</f>
-        <v>0</v>
+        <f>COUNTIFS($A$2:$A$49,$F$37,$C$2:$C$49,$F40,$D$2:$D$49,G$37)+MAX(C53-D53,0)</f>
+        <v>1</v>
       </c>
       <c r="H40" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$37,$C$2:$C$91,$F40,$D$2:$D$91,H$37)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$37,$C$2:$C$93,$F40,$D$2:$D$93,H$37)</f>
         <v>0</v>
       </c>
       <c r="I40" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$37,$C$2:$C$47,$F40,$D$2:$D$47,I$37) + MIN(C51,D51)</f>
-        <v>8</v>
+        <f>COUNTIFS($A$2:$A$49,$F$37,$C$2:$C$49,$F40,$D$2:$D$49,I$37) + MIN(C53,D53)</f>
+        <v>6</v>
       </c>
       <c r="J40" s="14">
-        <f t="shared" si="20"/>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="K40" s="14"/>
       <c r="L40" s="60" t="s">
@@ -21132,7 +21152,7 @@
       </c>
       <c r="M40" s="63">
         <f>(M38-M39)/(1-M39)</f>
-        <v>1</v>
+        <v>0.81355932203389825</v>
       </c>
       <c r="N40" s="65" t="s">
         <v>142</v>
@@ -21140,12 +21160,12 @@
     </row>
     <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A42</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A41</f>
+        <v>State</v>
       </c>
       <c r="B41" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B42</f>
-        <v>rising =&gt; baking</v>
+        <f>'Automatic Bread Maker Human-Bas'!B41</f>
+        <v>Rising</v>
       </c>
       <c r="C41" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C41</f>
@@ -21160,16 +21180,16 @@
         <v>143</v>
       </c>
       <c r="G41" s="14">
-        <f t="shared" ref="G41:I41" si="22">SUM(G38:G40)</f>
-        <v>3</v>
+        <f t="shared" ref="G41:I41" si="11">SUM(G38:G40)</f>
+        <v>5</v>
       </c>
       <c r="H41" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f t="shared" si="22"/>
-        <v>8</v>
+        <f t="shared" si="11"/>
+        <v>6</v>
       </c>
       <c r="J41" s="14"/>
       <c r="L41" s="14"/>
@@ -21177,61 +21197,61 @@
     </row>
     <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A42</f>
+        <v>Transition</v>
+      </c>
+      <c r="B42" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B42</f>
+        <v>rising =&gt; baking</v>
+      </c>
+      <c r="C42" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C42</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C42</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="49"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A43</f>
         <v>State</v>
       </c>
-      <c r="B42" s="5" t="str">
+      <c r="B43" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B43</f>
         <v>Baking</v>
       </c>
-      <c r="C42" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C42</f>
-        <v>1</v>
-      </c>
-      <c r="D42" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C42</f>
-        <v>1</v>
-      </c>
-      <c r="E42" s="49"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="5" t="str">
+      <c r="C43" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C43</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C43</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="49"/>
+      <c r="F43" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="L43" s="87" t="s">
+        <v>155</v>
+      </c>
+      <c r="M43" s="88"/>
+      <c r="N43" s="88"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A44</f>
         <v>Action</v>
       </c>
-      <c r="B43" s="5" t="str">
+      <c r="B44" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B44</f>
         <v>heat()</v>
-      </c>
-      <c r="C43" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C43</f>
-        <v>1</v>
-      </c>
-      <c r="D43" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C43</f>
-        <v>1</v>
-      </c>
-      <c r="E43" s="49"/>
-      <c r="F43" s="84" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="L43" s="86" t="s">
-        <v>155</v>
-      </c>
-      <c r="M43" s="87"/>
-      <c r="N43" s="87"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A45</f>
-        <v>Transition</v>
-      </c>
-      <c r="B44" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B45</f>
-        <v>baking =&gt; warming</v>
       </c>
       <c r="C44" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C44</f>
@@ -21270,12 +21290,12 @@
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A46</f>
-        <v>State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A45</f>
+        <v>Transition</v>
       </c>
       <c r="B45" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B46</f>
-        <v>Warming</v>
+        <f>'Automatic Bread Maker Human-Bas'!B45</f>
+        <v>baking =&gt; warming</v>
       </c>
       <c r="C45" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C45</f>
@@ -21290,19 +21310,19 @@
         <v>0</v>
       </c>
       <c r="G45" s="57">
-        <f t="shared" ref="G45:H45" si="23">COUNTIFS($A$2:$A$91,$F$44,$C$2:$C$91,$F45,$D$2:$D$91,G$44)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F45,$D$2:$D$93,G$44)</f>
         <v>2</v>
       </c>
       <c r="H45" s="58">
-        <f t="shared" si="23"/>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F45,$D$2:$D$93,H$44)</f>
         <v>0</v>
       </c>
       <c r="I45" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$44,$C$2:$C$47,$F45,$D$2:$D$47,I$44) + MAX(D54-C54,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$44,$C$2:$C$49,$F45,$D$2:$D$49,I$44) + MAX(D56-C56,0)</f>
         <v>0</v>
       </c>
       <c r="J45" s="14">
-        <f t="shared" ref="J45:J47" si="24">SUM(G45:I45)</f>
+        <f t="shared" ref="J45:J47" si="12">SUM(G45:I45)</f>
         <v>2</v>
       </c>
       <c r="K45" s="14"/>
@@ -21310,7 +21330,7 @@
         <v>138</v>
       </c>
       <c r="M45" s="57">
-        <f>(G45+H46+I47)/COUNTIF($A$2:$A$101,F44)</f>
+        <f>(G45+H46+I47)/COUNTIF($A$2:$A$103,F44)</f>
         <v>1</v>
       </c>
       <c r="N45" s="59" t="s">
@@ -21319,12 +21339,12 @@
     </row>
     <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A47</f>
-        <v>Action</v>
+        <f>'Automatic Bread Maker Human-Bas'!A46</f>
+        <v>State</v>
       </c>
       <c r="B46" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B47</f>
-        <v>warm()</v>
+        <f>'Automatic Bread Maker Human-Bas'!B46</f>
+        <v>Warming</v>
       </c>
       <c r="C46" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C46</f>
@@ -21339,19 +21359,19 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="61">
-        <f t="shared" ref="G46:I46" si="25">COUNTIFS($A$2:$A$91,$F$44,$C$2:$C$91,$F46,$D$2:$D$91,G$44)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F46,$D$2:$D$93,G$44)</f>
         <v>0</v>
       </c>
       <c r="H46" s="14">
-        <f t="shared" si="25"/>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F46,$D$2:$D$93,H$44)</f>
         <v>0</v>
       </c>
       <c r="I46" s="62">
-        <f t="shared" si="25"/>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F46,$D$2:$D$93,I$44)</f>
         <v>0</v>
       </c>
       <c r="J46" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K46" s="14"/>
@@ -21359,27 +21379,27 @@
         <v>140</v>
       </c>
       <c r="M46" s="61">
-        <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$101,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$101,F44))</f>
+        <f t="array" ref="M46">SUMPRODUCT(J45:J47/COUNTIF($A$2:$A$103,F44), TRANSPOSE(G48:I48)/COUNTIF($A$2:$A$103,F44))</f>
         <v>1</v>
       </c>
       <c r="N46" s="62" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A48</f>
-        <v>Transition</v>
+        <f>'Automatic Bread Maker Human-Bas'!A47</f>
+        <v>Action</v>
       </c>
       <c r="B47" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B48</f>
-        <v>adter 60min (warming =&gt; setup)</v>
-      </c>
-      <c r="C47" s="70">
+        <f>'Automatic Bread Maker Human-Bas'!B47</f>
+        <v>warm()</v>
+      </c>
+      <c r="C47" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C47</f>
         <v>1</v>
       </c>
-      <c r="D47" s="70">
+      <c r="D47" s="5">
         <f>'Automatic Bread Maker LLM-Based'!C47</f>
         <v>1</v>
       </c>
@@ -21388,19 +21408,19 @@
         <v>1</v>
       </c>
       <c r="G47" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$44,$C$2:$C$47,$F47,$D$2:$D$47,G$44) + MAX(C54-D54,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$44,$C$2:$C$49,$F47,$D$2:$D$49,G$44) + MAX(C56-D56,0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$44,$C$2:$C$91,$F47,$D$2:$D$91,H$44)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$44,$C$2:$C$93,$F47,$D$2:$D$93,H$44)</f>
         <v>0</v>
       </c>
       <c r="I47" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$44,$C$2:$C$47,$F47,$D$2:$D$47,I$44) + MIN(C54,D54)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$44,$C$2:$C$49,$F47,$D$2:$D$49,I$44) + MIN(C56,D56)</f>
         <v>0</v>
       </c>
       <c r="J47" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K47" s="14"/>
@@ -21416,19 +21436,19 @@
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="12" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A50</f>
-        <v>State</v>
-      </c>
-      <c r="B48" s="12" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B50</f>
-        <v>additional elements</v>
-      </c>
-      <c r="C48" s="12">
+      <c r="A48" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A48</f>
+        <v>Transition</v>
+      </c>
+      <c r="B48" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B48</f>
+        <v>adter 60min (warming =&gt; setup)</v>
+      </c>
+      <c r="C48" s="5">
         <f>'Automatic Bread Maker Human-Bas'!C48</f>
         <v>1</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="5">
         <f>'Automatic Bread Maker LLM-Based'!C48</f>
         <v>1</v>
       </c>
@@ -21437,15 +21457,15 @@
         <v>143</v>
       </c>
       <c r="G48" s="14">
-        <f t="shared" ref="G48:I48" si="26">SUM(G45:G47)</f>
+        <f t="shared" ref="G48:I48" si="13">SUM(G45:G47)</f>
         <v>2</v>
       </c>
       <c r="H48" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J48" s="14"/>
@@ -21453,61 +21473,61 @@
       <c r="M48" s="67"/>
     </row>
     <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="5" t="str">
+      <c r="A49" s="89" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A49</f>
+        <v>Transition</v>
+      </c>
+      <c r="B49" s="89" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B49</f>
+        <v>baking =&gt; setup</v>
+      </c>
+      <c r="C49" s="89">
+        <f>'Automatic Bread Maker Human-Bas'!C49</f>
+        <v>1</v>
+      </c>
+      <c r="D49" s="89">
+        <f>'Automatic Bread Maker LLM-Based'!C49</f>
+        <v>1</v>
+      </c>
+      <c r="E49" s="49"/>
+    </row>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A50</f>
+        <v>State</v>
+      </c>
+      <c r="B50" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B50</f>
+        <v>additional elements</v>
+      </c>
+      <c r="C50" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C50</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="49"/>
+      <c r="F50" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="L50" s="87" t="s">
+        <v>157</v>
+      </c>
+      <c r="M50" s="88"/>
+      <c r="N50" s="88"/>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!A51</f>
         <v>Transition</v>
       </c>
-      <c r="B49" s="5" t="str">
+      <c r="B51" s="5" t="str">
         <f>'Automatic Bread Maker Human-Bas'!B51</f>
-        <v>additional elements</v>
-      </c>
-      <c r="C49" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C49</f>
-        <v>1</v>
-      </c>
-      <c r="D49" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C49</f>
-        <v>1</v>
-      </c>
-      <c r="E49" s="49"/>
-    </row>
-    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A52</f>
-        <v>Guard</v>
-      </c>
-      <c r="B50" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B52</f>
-        <v>additional elements</v>
-      </c>
-      <c r="C50" s="5">
-        <f>'Automatic Bread Maker Human-Bas'!C50</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="5">
-        <f>'Automatic Bread Maker LLM-Based'!C50</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="49"/>
-      <c r="F50" s="84" t="s">
-        <v>156</v>
-      </c>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
-      <c r="L50" s="86" t="s">
-        <v>157</v>
-      </c>
-      <c r="M50" s="87"/>
-      <c r="N50" s="87"/>
-    </row>
-    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A53</f>
-        <v>Action</v>
-      </c>
-      <c r="B51" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B53</f>
         <v>additional elements</v>
       </c>
       <c r="C51" s="5">
@@ -21547,11 +21567,11 @@
     </row>
     <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A54</f>
-        <v>Composite State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A52</f>
+        <v>Guard</v>
       </c>
       <c r="B52" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B54</f>
+        <f>'Automatic Bread Maker Human-Bas'!B52</f>
         <v>additional elements</v>
       </c>
       <c r="C52" s="5">
@@ -21567,19 +21587,19 @@
         <v>0</v>
       </c>
       <c r="G52" s="57">
-        <f t="shared" ref="G52:H52" si="27">COUNTIFS($A$2:$A$91,$F$51,$C$2:$C$91,$F52,$D$2:$D$91,G$51)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F52,$D$2:$D$93,G$51)</f>
         <v>1</v>
       </c>
       <c r="H52" s="58">
-        <f t="shared" si="27"/>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F52,$D$2:$D$93,H$51)</f>
         <v>0</v>
       </c>
       <c r="I52" s="59">
-        <f>COUNTIFS($A$2:$A$47,$F$51,$C$2:$C$47,$F52,$D$2:$D$47,I$51)+MAX(D53-C53,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$51,$C$2:$C$49,$F52,$D$2:$D$49,I$51)+MAX(D55-C55,0)</f>
         <v>0</v>
       </c>
       <c r="J52" s="14">
-        <f t="shared" ref="J52:J54" si="28">SUM(G52:I52)</f>
+        <f t="shared" ref="J52:J54" si="14">SUM(G52:I52)</f>
         <v>1</v>
       </c>
       <c r="K52" s="14"/>
@@ -21587,7 +21607,7 @@
         <v>138</v>
       </c>
       <c r="M52" s="57">
-        <f>(G52+H53+I54)/COUNTIF($A$2:$A$101,F51)</f>
+        <f>(G52+H53+I54)/COUNTIF($A$2:$A$103,F51)</f>
         <v>1</v>
       </c>
       <c r="N52" s="59" t="s">
@@ -21596,11 +21616,11 @@
     </row>
     <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A55</f>
-        <v>Region</v>
+        <f>'Automatic Bread Maker Human-Bas'!A53</f>
+        <v>Action</v>
       </c>
       <c r="B53" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B55</f>
+        <f>'Automatic Bread Maker Human-Bas'!B53</f>
         <v>additional elements</v>
       </c>
       <c r="C53" s="5">
@@ -21616,19 +21636,19 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="61">
-        <f t="shared" ref="G53:I53" si="29">COUNTIFS($A$2:$A$91,$F$51,$C$2:$C$91,$F53,$D$2:$D$91,G$51)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F53,$D$2:$D$93,G$51)</f>
         <v>0</v>
       </c>
       <c r="H53" s="14">
-        <f t="shared" si="29"/>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F53,$D$2:$D$93,H$51)</f>
         <v>0</v>
       </c>
       <c r="I53" s="62">
-        <f t="shared" si="29"/>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F53,$D$2:$D$93,I$51)</f>
         <v>0</v>
       </c>
       <c r="J53" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K53" s="14"/>
@@ -21636,20 +21656,20 @@
         <v>140</v>
       </c>
       <c r="M53" s="61">
-        <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$101,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$101,F51))</f>
+        <f t="array" ref="M53">SUMPRODUCT(J52:J54/COUNTIF($A$2:$A$103,F51), TRANSPOSE(G55:I55)/COUNTIF($A$2:$A$103,F51))</f>
         <v>1</v>
       </c>
       <c r="N53" s="62" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!A56</f>
-        <v>History State</v>
+        <f>'Automatic Bread Maker Human-Bas'!A54</f>
+        <v>Composite State</v>
       </c>
       <c r="B54" s="5" t="str">
-        <f>'Automatic Bread Maker Human-Bas'!B56</f>
+        <f>'Automatic Bread Maker Human-Bas'!B54</f>
         <v>additional elements</v>
       </c>
       <c r="C54" s="5">
@@ -21665,19 +21685,19 @@
         <v>1</v>
       </c>
       <c r="G54" s="63">
-        <f>COUNTIFS($A$2:$A$47,$F$51,$C$2:$C$47,$F54,$D$2:$D$47,G$51) + MAX(C53-D53,0)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$51,$C$2:$C$49,$F54,$D$2:$D$49,G$51) + MAX(C55-D55,0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="64">
-        <f>COUNTIFS($A$2:$A$91,$F$51,$C$2:$C$91,$F54,$D$2:$D$91,H$51)</f>
+        <f>COUNTIFS($A$2:$A$93,$F$51,$C$2:$C$93,$F54,$D$2:$D$93,H$51)</f>
         <v>0</v>
       </c>
       <c r="I54" s="65">
-        <f>COUNTIFS($A$2:$A$47,$F$51,$C$2:$C$47,$F54,$D$2:$D$47,I$51)+MIN(C53,D53)</f>
+        <f>COUNTIFS($A$2:$A$49,$F$51,$C$2:$C$49,$F54,$D$2:$D$49,I$51)+MIN(C55,D55)</f>
         <v>0</v>
       </c>
       <c r="J54" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K54" s="14"/>
@@ -21693,24 +21713,36 @@
       </c>
     </row>
     <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="50"/>
-      <c r="B55" s="71"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
+      <c r="A55" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A55</f>
+        <v>Region</v>
+      </c>
+      <c r="B55" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B55</f>
+        <v>additional elements</v>
+      </c>
+      <c r="C55" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C55</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C55</f>
+        <v>0</v>
+      </c>
       <c r="E55" s="49"/>
       <c r="F55" s="66" t="s">
         <v>143</v>
       </c>
       <c r="G55" s="14">
-        <f t="shared" ref="G55:I55" si="30">SUM(G52:G54)</f>
+        <f t="shared" ref="G55:I55" si="15">SUM(G52:G54)</f>
         <v>1</v>
       </c>
       <c r="H55" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I55" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J55" s="14"/>
@@ -21718,10 +21750,22 @@
       <c r="M55" s="67"/>
     </row>
     <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="50"/>
-      <c r="B56" s="71"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
+      <c r="A56" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!A56</f>
+        <v>History State</v>
+      </c>
+      <c r="B56" s="5" t="str">
+        <f>'Automatic Bread Maker Human-Bas'!B56</f>
+        <v>additional elements</v>
+      </c>
+      <c r="C56" s="5">
+        <f>'Automatic Bread Maker Human-Bas'!C56</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="5">
+        <f>'Automatic Bread Maker LLM-Based'!C56</f>
+        <v>0</v>
+      </c>
       <c r="E56" s="49"/>
     </row>
     <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21866,32 +21910,42 @@
       <c r="D77" s="49"/>
     </row>
     <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="50"/>
       <c r="B78" s="71"/>
+      <c r="C78" s="49"/>
       <c r="D78" s="49"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="50"/>
       <c r="B79" s="71"/>
+      <c r="C79" s="49"/>
       <c r="D79" s="49"/>
     </row>
     <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="71"/>
       <c r="D80" s="49"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B81" s="71"/>
+      <c r="D81" s="49"/>
+    </row>
+    <row r="82" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D82" s="49"/>
+    </row>
+    <row r="83" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -22798,6 +22852,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -22808,12 +22868,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -22854,25 +22908,25 @@
       <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="88" t="s">
+      <c r="D1" s="82" t="s">
         <v>167</v>
       </c>
       <c r="E1" s="49"/>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="L1" s="84" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="L1" s="83" t="s">
         <v>158</v>
       </c>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="str">
@@ -23276,12 +23330,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="49"/>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="str">
@@ -23671,12 +23725,12 @@
         <v>0</v>
       </c>
       <c r="E15" s="49"/>
-      <c r="F15" s="84" t="s">
+      <c r="F15" s="83" t="s">
         <v>146</v>
       </c>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="str">
@@ -24066,12 +24120,12 @@
         <v>1</v>
       </c>
       <c r="E22" s="49"/>
-      <c r="F22" s="84" t="s">
+      <c r="F22" s="83" t="s">
         <v>148</v>
       </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="str">
@@ -24461,12 +24515,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="49"/>
-      <c r="F29" s="84" t="s">
+      <c r="F29" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="str">
@@ -24856,12 +24910,12 @@
         <v>1</v>
       </c>
       <c r="E36" s="49"/>
-      <c r="F36" s="84" t="s">
+      <c r="F36" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="str">
@@ -25251,12 +25305,12 @@
         <v>1</v>
       </c>
       <c r="E43" s="49"/>
-      <c r="F43" s="84" t="s">
+      <c r="F43" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="str">
@@ -25646,12 +25700,12 @@
         <v>0</v>
       </c>
       <c r="E50" s="49"/>
-      <c r="F50" s="84" t="s">
+      <c r="F50" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5" t="str">
